--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2636-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2636-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2991F299-2878-4AFC-AB9D-9386FBE0FA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{928C2E76-DA32-43BE-AD87-C611BB44A576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{BD399E11-B94F-4013-A182-2686814BA7E6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1804A1F8-9CF2-4777-BF50-AE914AECD202}"/>
   </bookViews>
   <sheets>
     <sheet name="2636-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1541,30 +1541,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7534A11-2210-4F78-A54A-07AB16D379A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C6444E-F796-4EE9-9A9A-A845E27DD95C}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1634,7 +1634,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1754,7 +1754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2023</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2022</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>8.27</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2020</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2019</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2018</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2017</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2016</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2015</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2014</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2013</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43"/>
       <c r="B25" s="44"/>
       <c r="C25" s="20" t="s">
@@ -3236,7 +3236,7 @@
       <c r="W25" s="50"/>
       <c r="X25" s="46"/>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2012</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2011</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2010</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2009</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2008</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2007</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2006</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37" t="s">
         <v>56</v>
       </c>
